--- a/Web/TestCases/PanelControl.xlsx
+++ b/Web/TestCases/PanelControl.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11775C57-3F64-4D38-90DB-B4571A9A81D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{510CF0CA-3C4A-433B-B38C-40E7D80D6A85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1425" yWindow="495" windowWidth="16815" windowHeight="12240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1275" yWindow="2460" windowWidth="26850" windowHeight="8040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
   <si>
     <t>Num</t>
   </si>
@@ -47,9 +47,6 @@
   </si>
   <si>
     <t>1. The Control Panel page is correctly.</t>
-  </si>
-  <si>
-    <t>The Control Panel page is correctly.</t>
   </si>
   <si>
     <t>https://drive.google.com/file/d/1nAERQz7NylVKp3-O6VJW9tZcGmua-6H9/view?usp=drive_link</t>
@@ -75,6 +72,12 @@
   </si>
   <si>
     <t>The user does not have the correct path. The "tenant" world must be translated.</t>
+  </si>
+  <si>
+    <t>pte</t>
+  </si>
+  <si>
+    <t>The Control Panel home.</t>
   </si>
 </sst>
 </file>
@@ -152,7 +155,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -175,12 +178,77 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="10">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF6565"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF6565"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -542,25 +610,25 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>11</v>
+        <v>16</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>10</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -568,13 +636,15 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
-      <c r="G3" s="2"/>
+      <c r="G3" s="8" t="s">
+        <v>17</v>
+      </c>
       <c r="H3" s="6"/>
     </row>
     <row r="4" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -582,13 +652,15 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
-      <c r="G4" s="2"/>
+      <c r="G4" s="8" t="s">
+        <v>17</v>
+      </c>
       <c r="H4" s="4"/>
     </row>
     <row r="5" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -596,23 +668,45 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
-      <c r="G5" s="2"/>
+      <c r="G5" s="8" t="s">
+        <v>17</v>
+      </c>
       <c r="H5" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
-  <conditionalFormatting sqref="G2:G5">
-    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="KO">
+  <conditionalFormatting sqref="G2">
+    <cfRule type="containsText" dxfId="7" priority="5" operator="containsText" text="PTE">
+      <formula>NOT(ISERROR(SEARCH("PTE",G2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="6" priority="6" operator="containsText" text="BL">
+      <formula>NOT(ISERROR(SEARCH("BL",G2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="5" priority="7" operator="containsText" text="KO">
       <formula>NOT(ISERROR(SEARCH("KO",G2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="OK">
+    <cfRule type="containsText" dxfId="4" priority="8" operator="containsText" text="OK">
       <formula>NOT(ISERROR(SEARCH("OK",G2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3:G5">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="PTE">
+      <formula>NOT(ISERROR(SEARCH("PTE",G3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="BL">
+      <formula>NOT(ISERROR(SEARCH("BL",G3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="KO">
+      <formula>NOT(ISERROR(SEARCH("KO",G3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="OK">
+      <formula>NOT(ISERROR(SEARCH("OK",G3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
